--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportPlanSummaryTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportPlanSummaryTemplate.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Báo cáo sản lượng" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ExportPlanSummaryTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ExportPlanSummaryTemplate.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Báo cáo sản lượng" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Báo cáo sản lượng'!$A$1:$C$1</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -383,6 +386,7 @@
       <c r="C1" s="1"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
